--- a/artfynd/A 41147-2025 artfynd.xlsx
+++ b/artfynd/A 41147-2025 artfynd.xlsx
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128884064</v>
+        <v>128889880</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,37 +1527,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514920</v>
+        <v>514841</v>
       </c>
       <c r="R10" t="n">
-        <v>6982193</v>
+        <v>6982213</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1584,19 +1584,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:50</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,44 +1601,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128889848</v>
+        <v>128889867</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>80048</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514751</v>
+        <v>514324</v>
       </c>
       <c r="R11" t="n">
-        <v>6982211</v>
+        <v>6982337</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1684,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128876118</v>
+        <v>128884064</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,42 +1721,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514584</v>
+        <v>514920</v>
       </c>
       <c r="R12" t="n">
-        <v>6982133</v>
+        <v>6982193</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1800,7 +1780,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1810,12 +1790,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gammal levande gran i stormfälld skog</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1830,60 +1805,60 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128889880</v>
+        <v>128884069</v>
       </c>
       <c r="B13" t="n">
-        <v>80144</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514841</v>
+        <v>514886</v>
       </c>
       <c r="R13" t="n">
-        <v>6982213</v>
+        <v>6982197</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1910,9 +1885,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>nr 5</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,57 +1917,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128889867</v>
+        <v>128869464</v>
       </c>
       <c r="B14" t="n">
-        <v>80048</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514324</v>
+        <v>514460</v>
       </c>
       <c r="R14" t="n">
-        <v>6982337</v>
+        <v>6982372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2007,9 +2006,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,48 +2045,48 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128884069</v>
+        <v>128874994</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>105717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514886</v>
+        <v>514353</v>
       </c>
       <c r="R15" t="n">
-        <v>6982197</v>
+        <v>6982209</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2106,7 +2115,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2116,12 +2125,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>nr 5</t>
+          <t>På marken i örtrik lövrik granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2136,66 +2145,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128869464</v>
+        <v>128889848</v>
       </c>
       <c r="B16" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514460</v>
+        <v>514751</v>
       </c>
       <c r="R16" t="n">
-        <v>6982372</v>
+        <v>6982211</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,19 +2225,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>08:33</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2264,45 +2259,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128874994</v>
+        <v>128876118</v>
       </c>
       <c r="B17" t="n">
-        <v>105717</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514353</v>
+        <v>514584</v>
       </c>
       <c r="R17" t="n">
-        <v>6982209</v>
+        <v>6982133</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På marken i örtrik lövrik granskog</t>
+          <t>Ringhack på gammal levande gran i stormfälld skog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -4407,10 +4407,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128878881</v>
+        <v>128884057</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4418,52 +4418,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>514548</v>
+        <v>514756</v>
       </c>
       <c r="R37" t="n">
-        <v>6982384</v>
+        <v>6982204</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4492,7 +4477,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4502,7 +4487,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,60 +4502,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128870217</v>
+        <v>128884052</v>
       </c>
       <c r="B38" t="n">
-        <v>80172</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>514470</v>
+        <v>514674</v>
       </c>
       <c r="R38" t="n">
-        <v>6982231</v>
+        <v>6982201</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4599,7 +4584,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4609,12 +4594,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På marken vid gammal gränssten i gammal tallskog</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,57 +4609,72 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128871304</v>
+        <v>128878881</v>
       </c>
       <c r="B39" t="n">
-        <v>75029</v>
+        <v>57725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>514323</v>
+        <v>514548</v>
       </c>
       <c r="R39" t="n">
-        <v>6982289</v>
+        <v>6982384</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4711,7 +4706,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4721,12 +4716,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På bark vid basen av gammal levande grov sälg</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4741,57 +4731,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128872163</v>
+        <v>128889908</v>
       </c>
       <c r="B40" t="n">
-        <v>80144</v>
+        <v>92206</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>514278</v>
+        <v>514334</v>
       </c>
       <c r="R40" t="n">
-        <v>6982253</v>
+        <v>6982213</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4821,24 +4811,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På klippa av granit under vårtbjörk</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4853,71 +4828,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128876502</v>
+        <v>128889830</v>
       </c>
       <c r="B41" t="n">
-        <v>98669</v>
+        <v>91533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>514606</v>
+        <v>514502</v>
       </c>
       <c r="R41" t="n">
-        <v>6982203</v>
+        <v>6982163</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4947,24 +4908,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>7 plantor inom 0,5x0,5 m i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4979,71 +4925,57 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128878425</v>
+        <v>128889839</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>91533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>514611</v>
+        <v>514333</v>
       </c>
       <c r="R42" t="n">
-        <v>6982407</v>
+        <v>6982363</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5073,19 +5005,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5100,66 +5022,57 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128873138</v>
+        <v>128889859</v>
       </c>
       <c r="B43" t="n">
-        <v>98669</v>
+        <v>92471</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>514250</v>
+        <v>514377</v>
       </c>
       <c r="R43" t="n">
-        <v>6982303</v>
+        <v>6982181</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5189,19 +5102,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>08:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5228,48 +5131,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128889908</v>
+        <v>128884068</v>
       </c>
       <c r="B44" t="n">
-        <v>92206</v>
+        <v>78705</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>898</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>514334</v>
+        <v>514902</v>
       </c>
       <c r="R44" t="n">
-        <v>6982213</v>
+        <v>6982190</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5296,9 +5199,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5313,57 +5226,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128889830</v>
+        <v>128870217</v>
       </c>
       <c r="B45" t="n">
-        <v>91533</v>
+        <v>80172</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6461</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>514502</v>
+        <v>514470</v>
       </c>
       <c r="R45" t="n">
-        <v>6982163</v>
+        <v>6982231</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5393,9 +5306,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På marken vid gammal gränssten i gammal tallskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5410,57 +5338,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128889839</v>
+        <v>128871304</v>
       </c>
       <c r="B46" t="n">
-        <v>91533</v>
+        <v>75029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>514333</v>
+        <v>514323</v>
       </c>
       <c r="R46" t="n">
-        <v>6982363</v>
+        <v>6982289</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5490,9 +5418,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande grov sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5507,57 +5450,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128889859</v>
+        <v>128872163</v>
       </c>
       <c r="B47" t="n">
-        <v>92471</v>
+        <v>80144</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>514377</v>
+        <v>514278</v>
       </c>
       <c r="R47" t="n">
-        <v>6982181</v>
+        <v>6982253</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5587,9 +5530,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På klippa av granit under vårtbjörk</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5604,60 +5562,74 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128884068</v>
+        <v>128876502</v>
       </c>
       <c r="B48" t="n">
-        <v>78705</v>
+        <v>98669</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>514902</v>
+        <v>514606</v>
       </c>
       <c r="R48" t="n">
-        <v>6982190</v>
+        <v>6982203</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5686,7 +5658,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5696,7 +5668,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>7 plantor inom 0,5x0,5 m i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5711,60 +5688,74 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128884057</v>
+        <v>128878425</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>514756</v>
+        <v>514611</v>
       </c>
       <c r="R49" t="n">
-        <v>6982204</v>
+        <v>6982407</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5793,7 +5784,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5803,7 +5794,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5818,60 +5809,69 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128884052</v>
+        <v>128873138</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>514674</v>
+        <v>514250</v>
       </c>
       <c r="R50" t="n">
-        <v>6982201</v>
+        <v>6982303</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5925,44 +5925,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128870181</v>
+        <v>128869313</v>
       </c>
       <c r="B51" t="n">
-        <v>91551</v>
+        <v>92826</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5972,10 +5972,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>514433</v>
+        <v>514473</v>
       </c>
       <c r="R51" t="n">
-        <v>6982337</v>
+        <v>6982357</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128884032</v>
+        <v>128870181</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>91551</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6055,37 +6055,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>514468</v>
+        <v>514433</v>
       </c>
       <c r="R52" t="n">
-        <v>6982207</v>
+        <v>6982337</v>
       </c>
       <c r="S52" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6139,19 +6139,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128884046</v>
+        <v>128884032</v>
       </c>
       <c r="B53" t="n">
         <v>79039</v>
@@ -6186,13 +6186,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>514578</v>
+        <v>514468</v>
       </c>
       <c r="R53" t="n">
-        <v>6982133</v>
+        <v>6982207</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6258,7 +6258,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128884059</v>
+        <v>128884046</v>
       </c>
       <c r="B54" t="n">
         <v>79039</v>
@@ -6293,10 +6293,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>514806</v>
+        <v>514578</v>
       </c>
       <c r="R54" t="n">
-        <v>6982209</v>
+        <v>6982133</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6328,7 +6328,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6365,7 +6365,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128884041</v>
+        <v>128884059</v>
       </c>
       <c r="B55" t="n">
         <v>79039</v>
@@ -6400,10 +6400,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>514544</v>
+        <v>514806</v>
       </c>
       <c r="R55" t="n">
-        <v>6982139</v>
+        <v>6982209</v>
       </c>
       <c r="S55" t="n">
         <v>4</v>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6445,7 +6445,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6472,7 +6472,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128872870</v>
+        <v>128884041</v>
       </c>
       <c r="B56" t="n">
         <v>79039</v>
@@ -6503,17 +6503,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>514274</v>
+        <v>514544</v>
       </c>
       <c r="R56" t="n">
-        <v>6982277</v>
+        <v>6982139</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6552,12 +6552,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal lövrik barrblandskog</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6572,22 +6567,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128877632</v>
+        <v>128872870</v>
       </c>
       <c r="B57" t="n">
-        <v>78442</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6595,21 +6590,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6619,10 +6614,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>514913</v>
+        <v>514274</v>
       </c>
       <c r="R57" t="n">
-        <v>6982190</v>
+        <v>6982277</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6654,7 +6649,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6664,12 +6659,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På ved på grov gammal tallhögstubbe i gammal, 200-årig tallskog</t>
+          <t>På gammal gran i gammal lövrik barrblandskog</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6696,32 +6691,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128889895</v>
+        <v>128889855</v>
       </c>
       <c r="B58" t="n">
-        <v>80104</v>
+        <v>57725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6731,10 +6726,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>514849</v>
+        <v>514496</v>
       </c>
       <c r="R58" t="n">
-        <v>6982221</v>
+        <v>6982422</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6767,6 +6762,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6793,45 +6793,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128872769</v>
+        <v>128889864</v>
       </c>
       <c r="B59" t="n">
-        <v>80189</v>
+        <v>80048</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229504</v>
+        <v>6456</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grynig filtlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Peltigera collina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Schrad.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>514269</v>
+        <v>514509</v>
       </c>
       <c r="R59" t="n">
-        <v>6982269</v>
+        <v>6982170</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6861,24 +6861,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På klippvägg av granit</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6893,57 +6878,57 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128869313</v>
+        <v>128889827</v>
       </c>
       <c r="B60" t="n">
-        <v>92826</v>
+        <v>79658</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>514473</v>
+        <v>514264</v>
       </c>
       <c r="R60" t="n">
-        <v>6982357</v>
+        <v>6982277</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6973,19 +6958,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>08:33</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7012,32 +6987,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128889855</v>
+        <v>128889894</v>
       </c>
       <c r="B61" t="n">
-        <v>57725</v>
+        <v>80180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7047,10 +7022,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>514496</v>
+        <v>514841</v>
       </c>
       <c r="R61" t="n">
-        <v>6982422</v>
+        <v>6982215</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7083,11 +7058,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7114,45 +7084,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128889864</v>
+        <v>128877632</v>
       </c>
       <c r="B62" t="n">
-        <v>80048</v>
+        <v>78442</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>514509</v>
+        <v>514913</v>
       </c>
       <c r="R62" t="n">
-        <v>6982170</v>
+        <v>6982190</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7182,9 +7152,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På ved på grov gammal tallhögstubbe i gammal, 200-årig tallskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7199,60 +7184,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128889827</v>
+        <v>128884033</v>
       </c>
       <c r="B63" t="n">
-        <v>79658</v>
+        <v>98669</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>514264</v>
+        <v>514476</v>
       </c>
       <c r="R63" t="n">
-        <v>6982277</v>
+        <v>6982199</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7279,74 +7264,104 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>nr 40</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128889894</v>
+        <v>128870176</v>
       </c>
       <c r="B64" t="n">
-        <v>80180</v>
+        <v>98669</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>514841</v>
+        <v>514446</v>
       </c>
       <c r="R64" t="n">
-        <v>6982215</v>
+        <v>6982269</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7376,9 +7391,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>28 plantor inom 1x1 m på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7393,19 +7423,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128884033</v>
+        <v>128870653</v>
       </c>
       <c r="B65" t="n">
         <v>98669</v>
@@ -7433,20 +7463,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>514476</v>
+        <v>514397</v>
       </c>
       <c r="R65" t="n">
-        <v>6982199</v>
+        <v>6982246</v>
       </c>
       <c r="S65" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7475,7 +7519,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7485,12 +7529,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:16</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>nr 40</t>
+          <t>På marken i gammal barrblandskog, 9 plantor inom 2x1 m</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7499,78 +7543,63 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128870176</v>
+        <v>128889895</v>
       </c>
       <c r="B66" t="n">
-        <v>98669</v>
+        <v>80104</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>514446</v>
+        <v>514849</v>
       </c>
       <c r="R66" t="n">
-        <v>6982269</v>
+        <v>6982221</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7600,24 +7629,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>28 plantor inom 1x1 m på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7632,71 +7646,57 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128870653</v>
+        <v>128872769</v>
       </c>
       <c r="B67" t="n">
-        <v>98669</v>
+        <v>80189</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>229504</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grynig filtlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Peltigera collina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Schrad.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>514397</v>
+        <v>514269</v>
       </c>
       <c r="R67" t="n">
-        <v>6982246</v>
+        <v>6982269</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>På marken i gammal barrblandskog, 9 plantor inom 2x1 m</t>
+          <t>På klippvägg av granit</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7867,45 +7867,59 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128875958</v>
+        <v>128869349</v>
       </c>
       <c r="B69" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>514529</v>
+        <v>514537</v>
       </c>
       <c r="R69" t="n">
-        <v>6982140</v>
+        <v>6982305</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7937,7 +7951,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7947,7 +7961,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>8 plantor inom 1x1 m, på marken i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7962,57 +7981,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128889847</v>
+        <v>128876974</v>
       </c>
       <c r="B70" t="n">
-        <v>57725</v>
+        <v>80104</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>514811</v>
+        <v>514782</v>
       </c>
       <c r="R70" t="n">
-        <v>6982193</v>
+        <v>6982203</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8042,14 +8061,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8064,57 +8093,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128889846</v>
+        <v>128871538</v>
       </c>
       <c r="B71" t="n">
-        <v>57725</v>
+        <v>91586</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>514833</v>
+        <v>514311</v>
       </c>
       <c r="R71" t="n">
-        <v>6982209</v>
+        <v>6982268</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8144,14 +8173,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>09:59</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>På bark på stam av död asp</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8166,22 +8205,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128889892</v>
+        <v>128875958</v>
       </c>
       <c r="B72" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8189,34 +8228,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>514340</v>
+        <v>514529</v>
       </c>
       <c r="R72" t="n">
-        <v>6982308</v>
+        <v>6982140</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8246,9 +8285,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8275,10 +8324,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128884065</v>
+        <v>128889846</v>
       </c>
       <c r="B73" t="n">
-        <v>78442</v>
+        <v>57725</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8286,37 +8335,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>514939</v>
+        <v>514833</v>
       </c>
       <c r="R73" t="n">
-        <v>6982199</v>
+        <v>6982209</v>
       </c>
       <c r="S73" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8343,19 +8392,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:55</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8370,71 +8414,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128869349</v>
+        <v>128889847</v>
       </c>
       <c r="B74" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>514537</v>
+        <v>514811</v>
       </c>
       <c r="R74" t="n">
-        <v>6982305</v>
+        <v>6982193</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8464,24 +8494,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>8 plantor inom 1x1 m, på marken i gammal barrblandskog</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8496,57 +8516,57 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128876974</v>
+        <v>128889892</v>
       </c>
       <c r="B75" t="n">
-        <v>80104</v>
+        <v>80144</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>514782</v>
+        <v>514340</v>
       </c>
       <c r="R75" t="n">
-        <v>6982203</v>
+        <v>6982308</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8576,24 +8596,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På gammal asp</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8608,60 +8613,60 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128871538</v>
+        <v>128884065</v>
       </c>
       <c r="B76" t="n">
-        <v>91586</v>
+        <v>78442</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5321</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>514311</v>
+        <v>514939</v>
       </c>
       <c r="R76" t="n">
-        <v>6982268</v>
+        <v>6982199</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8690,7 +8695,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8700,12 +8705,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:59</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På bark på stam av död asp</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8720,12 +8720,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9644,32 +9644,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128869375</v>
+        <v>128875180</v>
       </c>
       <c r="B85" t="n">
-        <v>78052</v>
+        <v>91988</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228579</v>
+        <v>1209</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>514562</v>
+        <v>514348</v>
       </c>
       <c r="R85" t="n">
-        <v>6982318</v>
+        <v>6982181</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
+          <t>På bark på granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9756,10 +9756,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128875180</v>
+        <v>128875123</v>
       </c>
       <c r="B86" t="n">
-        <v>91988</v>
+        <v>92206</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9767,21 +9767,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>514348</v>
+        <v>514330</v>
       </c>
       <c r="R86" t="n">
-        <v>6982181</v>
+        <v>6982223</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9826,7 +9826,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9836,12 +9836,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På bark på granlåga i gammal bördig granskog</t>
+          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9868,45 +9868,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128875123</v>
+        <v>128889837</v>
       </c>
       <c r="B87" t="n">
-        <v>92206</v>
+        <v>91533</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>514330</v>
+        <v>514358</v>
       </c>
       <c r="R87" t="n">
-        <v>6982223</v>
+        <v>6982358</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9936,24 +9936,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:32</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På granlåga i gammal bördig granskog</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9968,22 +9953,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128889837</v>
+        <v>128870269</v>
       </c>
       <c r="B88" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9991,34 +9976,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>514358</v>
+        <v>514480</v>
       </c>
       <c r="R88" t="n">
-        <v>6982358</v>
+        <v>6982222</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10048,9 +10033,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla tallar och granar i gammal tallskog</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10065,19 +10065,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128870269</v>
+        <v>128884058</v>
       </c>
       <c r="B89" t="n">
         <v>79039</v>
@@ -10108,17 +10108,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>514480</v>
+        <v>514781</v>
       </c>
       <c r="R89" t="n">
-        <v>6982222</v>
+        <v>6982207</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10157,12 +10157,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla tallar och granar i gammal tallskog</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10177,22 +10172,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128884058</v>
+        <v>128889843</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10200,37 +10195,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>514781</v>
+        <v>514508</v>
       </c>
       <c r="R90" t="n">
-        <v>6982207</v>
+        <v>6982488</v>
       </c>
       <c r="S90" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10257,19 +10252,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>13:09</t>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10284,57 +10274,57 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128889843</v>
+        <v>128869525</v>
       </c>
       <c r="B91" t="n">
-        <v>57725</v>
+        <v>80079</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6457</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>514508</v>
+        <v>514545</v>
       </c>
       <c r="R91" t="n">
-        <v>6982488</v>
+        <v>6982299</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10364,14 +10354,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>08:59</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På bark på stam av levande gammal grov asp (60 cm dbh) i gammal lövrik granskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10386,22 +10386,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128869525</v>
+        <v>128869600</v>
       </c>
       <c r="B92" t="n">
-        <v>80079</v>
+        <v>80172</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10409,21 +10409,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6457</v>
+        <v>6461</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>514545</v>
+        <v>514448</v>
       </c>
       <c r="R92" t="n">
-        <v>6982299</v>
+        <v>6982331</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10478,12 +10478,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>08:59</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal grov asp (60 cm dbh) i gammal lövrik granskog</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10498,60 +10493,60 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128869600</v>
+        <v>128884049</v>
       </c>
       <c r="B93" t="n">
-        <v>80172</v>
+        <v>80144</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>514448</v>
+        <v>514588</v>
       </c>
       <c r="R93" t="n">
-        <v>6982331</v>
+        <v>6982187</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10580,7 +10575,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10590,7 +10585,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10605,19 +10600,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128884049</v>
+        <v>128889882</v>
       </c>
       <c r="B94" t="n">
         <v>80144</v>
@@ -10648,17 +10643,17 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>514588</v>
+        <v>514603</v>
       </c>
       <c r="R94" t="n">
-        <v>6982187</v>
+        <v>6982204</v>
       </c>
       <c r="S94" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10685,19 +10680,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>12:40</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10712,57 +10697,57 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128889882</v>
+        <v>128869461</v>
       </c>
       <c r="B95" t="n">
-        <v>80144</v>
+        <v>80048</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>514603</v>
+        <v>514553</v>
       </c>
       <c r="R95" t="n">
-        <v>6982204</v>
+        <v>6982298</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10792,11 +10777,26 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
@@ -10805,48 +10805,63 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128869461</v>
+        <v>128869225</v>
       </c>
       <c r="B96" t="n">
-        <v>80048</v>
+        <v>78796</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10856,10 +10871,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>514553</v>
+        <v>514501</v>
       </c>
       <c r="R96" t="n">
-        <v>6982298</v>
+        <v>6982395</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10891,7 +10906,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10901,12 +10916,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10917,21 +10932,6 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -10948,10 +10948,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128869225</v>
+        <v>128869375</v>
       </c>
       <c r="B97" t="n">
-        <v>78796</v>
+        <v>78052</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10959,21 +10959,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>228579</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10983,10 +10983,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>514501</v>
+        <v>514562</v>
       </c>
       <c r="R97" t="n">
-        <v>6982395</v>
+        <v>6982318</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11028,12 +11028,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>På kolad tallstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -13799,48 +13799,48 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128869178</v>
+        <v>128884030</v>
       </c>
       <c r="B124" t="n">
-        <v>91305</v>
+        <v>91547</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3215</v>
+        <v>1204</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>514489</v>
+        <v>514458</v>
       </c>
       <c r="R124" t="n">
-        <v>6982416</v>
+        <v>6982209</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13879,12 +13879,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>08:31</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>I gammal barrblandskog</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13899,12 +13894,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
@@ -14018,10 +14013,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128889853</v>
+        <v>128877603</v>
       </c>
       <c r="B126" t="n">
-        <v>57725</v>
+        <v>79629</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14029,34 +14024,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>514661</v>
+        <v>514913</v>
       </c>
       <c r="R126" t="n">
-        <v>6982181</v>
+        <v>6982190</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14086,14 +14081,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>På grov gammal tallhögstubbe (50 cm dbh) i gammal tallskog</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14108,62 +14113,57 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128870907</v>
+        <v>128889869</v>
       </c>
       <c r="B127" t="n">
-        <v>57725</v>
+        <v>91988</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>514334</v>
+        <v>514384</v>
       </c>
       <c r="R127" t="n">
-        <v>6982242</v>
+        <v>6982187</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14193,19 +14193,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>08:33</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14232,45 +14222,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128872298</v>
+        <v>128889840</v>
       </c>
       <c r="B128" t="n">
-        <v>80179</v>
+        <v>91533</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>514278</v>
+        <v>514369</v>
       </c>
       <c r="R128" t="n">
-        <v>6982253</v>
+        <v>6982338</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14300,24 +14290,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>10:14</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>På granitklippa under vårtbjörk i brant</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14332,60 +14307,60 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128884074</v>
+        <v>128869178</v>
       </c>
       <c r="B129" t="n">
-        <v>98669</v>
+        <v>91305</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>514780</v>
+        <v>514489</v>
       </c>
       <c r="R129" t="n">
-        <v>6982321</v>
+        <v>6982416</v>
       </c>
       <c r="S129" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14414,7 +14389,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14424,12 +14399,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>nr 20</t>
+          <t>I gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14444,71 +14419,57 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128878320</v>
+        <v>128889853</v>
       </c>
       <c r="B130" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>514646</v>
+        <v>514661</v>
       </c>
       <c r="R130" t="n">
-        <v>6982381</v>
+        <v>6982181</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14538,24 +14499,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>135 plantor inom 2x2 m i gammal tätvuxen granskog</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14570,60 +14521,65 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128884051</v>
+        <v>128870907</v>
       </c>
       <c r="B131" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>514602</v>
+        <v>514334</v>
       </c>
       <c r="R131" t="n">
-        <v>6982211</v>
+        <v>6982242</v>
       </c>
       <c r="S131" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14652,7 +14608,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14662,12 +14618,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>nr 30</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14682,60 +14633,60 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128884071</v>
+        <v>128869301</v>
       </c>
       <c r="B132" t="n">
-        <v>98669</v>
+        <v>79039</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>514808</v>
+        <v>514493</v>
       </c>
       <c r="R132" t="n">
-        <v>6982305</v>
+        <v>6982326</v>
       </c>
       <c r="S132" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14764,7 +14715,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14774,12 +14725,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>nr 30</t>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14794,60 +14745,60 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128884031</v>
+        <v>128872298</v>
       </c>
       <c r="B133" t="n">
-        <v>98669</v>
+        <v>80179</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>514458</v>
+        <v>514278</v>
       </c>
       <c r="R133" t="n">
-        <v>6982208</v>
+        <v>6982253</v>
       </c>
       <c r="S133" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14876,7 +14827,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14886,12 +14837,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>nr 20</t>
+          <t>På granitklippa under vårtbjörk i brant</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14906,19 +14857,19 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128871633</v>
+        <v>128884074</v>
       </c>
       <c r="B134" t="n">
         <v>98669</v>
@@ -14946,29 +14897,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>514310</v>
+        <v>514780</v>
       </c>
       <c r="R134" t="n">
-        <v>6982246</v>
+        <v>6982321</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14997,7 +14939,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15007,12 +14949,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Inom 2x1 m</t>
+          <t>nr 20</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15027,22 +14969,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128889869</v>
+        <v>128878320</v>
       </c>
       <c r="B135" t="n">
-        <v>91988</v>
+        <v>98669</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15050,34 +14992,48 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>514384</v>
+        <v>514646</v>
       </c>
       <c r="R135" t="n">
-        <v>6982187</v>
+        <v>6982381</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15107,9 +15063,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>135 plantor inom 2x2 m i gammal tätvuxen granskog</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15124,60 +15095,60 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128889840</v>
+        <v>128884051</v>
       </c>
       <c r="B136" t="n">
-        <v>91533</v>
+        <v>98669</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>514369</v>
+        <v>514602</v>
       </c>
       <c r="R136" t="n">
-        <v>6982338</v>
+        <v>6982211</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15204,9 +15175,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>nr 30</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15221,44 +15207,44 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128884030</v>
+        <v>128884071</v>
       </c>
       <c r="B137" t="n">
-        <v>91547</v>
+        <v>98669</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15268,10 +15254,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>514458</v>
+        <v>514808</v>
       </c>
       <c r="R137" t="n">
-        <v>6982209</v>
+        <v>6982305</v>
       </c>
       <c r="S137" t="n">
         <v>4</v>
@@ -15303,7 +15289,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15313,7 +15299,12 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>nr 30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15340,48 +15331,48 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128869301</v>
+        <v>128884031</v>
       </c>
       <c r="B138" t="n">
-        <v>79039</v>
+        <v>98669</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>514493</v>
+        <v>514458</v>
       </c>
       <c r="R138" t="n">
-        <v>6982326</v>
+        <v>6982208</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15410,7 +15401,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15420,12 +15411,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>nr 20</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15440,57 +15431,66 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128877603</v>
+        <v>128871633</v>
       </c>
       <c r="B139" t="n">
-        <v>79629</v>
+        <v>98669</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>514913</v>
+        <v>514310</v>
       </c>
       <c r="R139" t="n">
-        <v>6982190</v>
+        <v>6982246</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15522,7 +15522,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15532,12 +15532,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>På grov gammal tallhögstubbe (50 cm dbh) i gammal tallskog</t>
+          <t>Inom 2x1 m</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18326,10 +18326,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128889860</v>
+        <v>128884035</v>
       </c>
       <c r="B165" t="n">
-        <v>57722</v>
+        <v>80145</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18337,37 +18337,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>514522</v>
+        <v>514511</v>
       </c>
       <c r="R165" t="n">
-        <v>6982392</v>
+        <v>6982178</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18394,14 +18394,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Lockläte</t>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18416,12 +18421,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
@@ -18928,10 +18933,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128889893</v>
+        <v>128889860</v>
       </c>
       <c r="B171" t="n">
-        <v>80144</v>
+        <v>57722</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18939,21 +18944,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18963,10 +18968,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>514306</v>
+        <v>514522</v>
       </c>
       <c r="R171" t="n">
-        <v>6982373</v>
+        <v>6982392</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18999,6 +19004,11 @@
       <c r="AA171" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>Lockläte</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19025,10 +19035,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128884060</v>
+        <v>128889893</v>
       </c>
       <c r="B172" t="n">
-        <v>79039</v>
+        <v>80144</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19036,37 +19046,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>514842</v>
+        <v>514306</v>
       </c>
       <c r="R172" t="n">
-        <v>6982222</v>
+        <v>6982373</v>
       </c>
       <c r="S172" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19093,24 +19103,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>nr 500</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19125,22 +19120,22 @@
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128884035</v>
+        <v>128884060</v>
       </c>
       <c r="B173" t="n">
-        <v>80145</v>
+        <v>79039</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19148,21 +19143,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19172,10 +19167,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>514511</v>
+        <v>514842</v>
       </c>
       <c r="R173" t="n">
-        <v>6982178</v>
+        <v>6982222</v>
       </c>
       <c r="S173" t="n">
         <v>4</v>
@@ -19207,7 +19202,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19217,7 +19212,12 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>nr 500</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20642,10 +20642,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>128884075</v>
+        <v>128873192</v>
       </c>
       <c r="B187" t="n">
-        <v>79039</v>
+        <v>80010</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20653,37 +20653,37 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>388</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Collema furfuraceum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Arnold) Du Rietz</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>514760</v>
+        <v>514251</v>
       </c>
       <c r="R187" t="n">
-        <v>6982345</v>
+        <v>6982323</v>
       </c>
       <c r="S187" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20722,7 +20722,12 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20737,19 +20742,19 @@
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128889902</v>
+        <v>128884075</v>
       </c>
       <c r="B188" t="n">
         <v>79039</v>
@@ -20780,17 +20785,17 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>514491</v>
+        <v>514760</v>
       </c>
       <c r="R188" t="n">
-        <v>6982221</v>
+        <v>6982345</v>
       </c>
       <c r="S188" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -20817,9 +20822,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20834,19 +20849,19 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>128884020</v>
+        <v>128889902</v>
       </c>
       <c r="B189" t="n">
         <v>79039</v>
@@ -20877,17 +20892,17 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>514453</v>
+        <v>514491</v>
       </c>
       <c r="R189" t="n">
-        <v>6982412</v>
+        <v>6982221</v>
       </c>
       <c r="S189" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -20914,19 +20929,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -20941,22 +20946,22 @@
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128889887</v>
+        <v>128884020</v>
       </c>
       <c r="B190" t="n">
-        <v>80144</v>
+        <v>79039</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -20964,37 +20969,37 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>514231</v>
+        <v>514453</v>
       </c>
       <c r="R190" t="n">
-        <v>6982325</v>
+        <v>6982412</v>
       </c>
       <c r="S190" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -21021,9 +21026,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB190" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21038,22 +21053,22 @@
       <c r="AT190" t="inlineStr"/>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>128873192</v>
+        <v>128889887</v>
       </c>
       <c r="B191" t="n">
-        <v>80010</v>
+        <v>80144</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21061,34 +21076,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>388</v>
+        <v>6458</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Collema furfuraceum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Arnold) Du Rietz</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>514251</v>
+        <v>514231</v>
       </c>
       <c r="R191" t="n">
-        <v>6982323</v>
+        <v>6982325</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21118,24 +21133,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z191" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB191" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21150,44 +21150,44 @@
       <c r="AT191" t="inlineStr"/>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>128873127</v>
+        <v>128877171</v>
       </c>
       <c r="B192" t="n">
-        <v>80144</v>
+        <v>79295</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21197,10 +21197,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>514246</v>
+        <v>514843</v>
       </c>
       <c r="R192" t="n">
-        <v>6982310</v>
+        <v>6982220</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21232,7 +21232,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21242,12 +21242,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AC192" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp</t>
+          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21274,32 +21274,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128877171</v>
+        <v>128873127</v>
       </c>
       <c r="B193" t="n">
-        <v>79295</v>
+        <v>80144</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21309,10 +21309,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>514843</v>
+        <v>514246</v>
       </c>
       <c r="R193" t="n">
-        <v>6982220</v>
+        <v>6982310</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21354,12 +21354,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal sälg i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21860,10 +21860,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128889838</v>
+        <v>128889850</v>
       </c>
       <c r="B198" t="n">
-        <v>91533</v>
+        <v>57725</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21871,21 +21871,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21895,10 +21895,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>514335</v>
+        <v>514487</v>
       </c>
       <c r="R198" t="n">
-        <v>6982363</v>
+        <v>6982442</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21931,6 +21931,11 @@
       <c r="AA198" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21957,10 +21962,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>128872887</v>
+        <v>128889842</v>
       </c>
       <c r="B199" t="n">
-        <v>79071</v>
+        <v>57725</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -21968,34 +21973,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>185</v>
+        <v>100109</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>514274</v>
+        <v>514529</v>
       </c>
       <c r="R199" t="n">
-        <v>6982277</v>
+        <v>6982505</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22025,24 +22030,14 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z199" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AB199" t="inlineStr">
-        <is>
-          <t>10:28</t>
-        </is>
-      </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal barrblandskog</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22057,60 +22052,60 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>128884021</v>
+        <v>128889896</v>
       </c>
       <c r="B200" t="n">
-        <v>96915</v>
+        <v>80104</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>53</v>
+        <v>229497</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>514456</v>
+        <v>514273</v>
       </c>
       <c r="R200" t="n">
-        <v>6982407</v>
+        <v>6982286</v>
       </c>
       <c r="S200" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -22137,19 +22132,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>11:43</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>11:43</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22164,60 +22149,60 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>128889842</v>
+        <v>128884077</v>
       </c>
       <c r="B201" t="n">
-        <v>57725</v>
+        <v>98669</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>514529</v>
+        <v>514653</v>
       </c>
       <c r="R201" t="n">
-        <v>6982505</v>
+        <v>6982356</v>
       </c>
       <c r="S201" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -22244,14 +22229,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>nr 40</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22266,57 +22261,66 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128872634</v>
+        <v>128869591</v>
       </c>
       <c r="B202" t="n">
-        <v>79125</v>
+        <v>98669</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6450</v>
+        <v>220787</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P202" t="inlineStr">
         <is>
           <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>514262</v>
+        <v>514450</v>
       </c>
       <c r="R202" t="n">
-        <v>6982252</v>
+        <v>6982333</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22348,7 +22352,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22358,12 +22362,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>På sydvänd klippa av granit i gammal tallskog</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22378,57 +22377,66 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128871645</v>
+        <v>128871502</v>
       </c>
       <c r="B203" t="n">
-        <v>79658</v>
+        <v>98669</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P203" t="inlineStr">
         <is>
           <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>514307</v>
+        <v>514298</v>
       </c>
       <c r="R203" t="n">
-        <v>6982260</v>
+        <v>6982273</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22460,7 +22468,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22470,12 +22478,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>10:06</t>
-        </is>
-      </c>
-      <c r="AC203" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallrot i gammal tallskog vid brant</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22490,60 +22493,60 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128884039</v>
+        <v>128889836</v>
       </c>
       <c r="B204" t="n">
-        <v>80173</v>
+        <v>91533</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>514523</v>
+        <v>514348</v>
       </c>
       <c r="R204" t="n">
-        <v>6982153</v>
+        <v>6982321</v>
       </c>
       <c r="S204" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -22570,19 +22573,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z204" t="inlineStr">
-        <is>
-          <t>12:24</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB204" t="inlineStr">
-        <is>
-          <t>12:24</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22597,57 +22590,57 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128873118</v>
+        <v>128889838</v>
       </c>
       <c r="B205" t="n">
-        <v>80179</v>
+        <v>91533</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>514246</v>
+        <v>514335</v>
       </c>
       <c r="R205" t="n">
-        <v>6982310</v>
+        <v>6982363</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22677,24 +22670,9 @@
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="Z205" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>2025-10-03</t>
-        </is>
-      </c>
-      <c r="AB205" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22709,66 +22687,57 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128869591</v>
+        <v>128872887</v>
       </c>
       <c r="B206" t="n">
-        <v>98669</v>
+        <v>79071</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J206" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
           <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>514450</v>
+        <v>514274</v>
       </c>
       <c r="R206" t="n">
-        <v>6982333</v>
+        <v>6982277</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22800,7 +22769,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22810,7 +22779,12 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>10:28</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22825,69 +22799,60 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128871502</v>
+        <v>128884021</v>
       </c>
       <c r="B207" t="n">
-        <v>98669</v>
+        <v>96915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I207" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Värsjöberget, Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>514298</v>
+        <v>514456</v>
       </c>
       <c r="R207" t="n">
-        <v>6982273</v>
+        <v>6982407</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -22916,7 +22881,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22926,7 +22891,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22941,60 +22906,60 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128884077</v>
+        <v>128872634</v>
       </c>
       <c r="B208" t="n">
-        <v>98669</v>
+        <v>79125</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>6450</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>värsjön, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>514653</v>
+        <v>514262</v>
       </c>
       <c r="R208" t="n">
-        <v>6982356</v>
+        <v>6982252</v>
       </c>
       <c r="S208" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -23023,7 +22988,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23033,12 +22998,12 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC208" t="inlineStr">
         <is>
-          <t>nr 40</t>
+          <t>På sydvänd klippa av granit i gammal tallskog</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23053,22 +23018,22 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128889836</v>
+        <v>128871645</v>
       </c>
       <c r="B209" t="n">
-        <v>91533</v>
+        <v>79658</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23076,34 +23041,34 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>514348</v>
+        <v>514307</v>
       </c>
       <c r="R209" t="n">
-        <v>6982321</v>
+        <v>6982260</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23133,9 +23098,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB209" t="inlineStr">
+        <is>
+          <t>10:06</t>
+        </is>
+      </c>
+      <c r="AC209" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallrot i gammal tallskog vid brant</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23150,60 +23130,60 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128889850</v>
+        <v>128884039</v>
       </c>
       <c r="B210" t="n">
-        <v>57725</v>
+        <v>80173</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>värsjön, Jmt</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>514487</v>
+        <v>514523</v>
       </c>
       <c r="R210" t="n">
-        <v>6982442</v>
+        <v>6982153</v>
       </c>
       <c r="S210" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -23230,14 +23210,19 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>2025-10-03</t>
         </is>
       </c>
-      <c r="AC210" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23252,22 +23237,22 @@
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128889896</v>
+        <v>128873118</v>
       </c>
       <c r="B211" t="n">
-        <v>80104</v>
+        <v>80179</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23275,34 +23260,34 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Värsjöberget, Jmt</t>
+          <t>Värsjöberget, Värsjöberget, Jmt</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>514273</v>
+        <v>514246</v>
       </c>
       <c r="R211" t="n">
-        <v>6982286</v>
+        <v>6982310</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23332,9 +23317,24 @@
           <t>2025-10-03</t>
         </is>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="AB211" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23349,12 +23349,12 @@
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>

--- a/artfynd/A 41147-2025 artfynd.xlsx
+++ b/artfynd/A 41147-2025 artfynd.xlsx
@@ -1203,7 +1203,7 @@
         <v>128889854</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,12 +1290,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
         <v>128869125</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>128889852</v>
       </c>
       <c r="B9" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1504,12 +1504,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1820,7 +1820,7 @@
         <v>128889848</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,12 +1907,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1922,7 +1922,7 @@
         <v>128876118</v>
       </c>
       <c r="B14" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>128878881</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5267,12 +5267,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -7089,7 +7089,7 @@
         <v>128889855</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7176,12 +7176,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -8523,7 +8523,7 @@
         <v>128889847</v>
       </c>
       <c r="B75" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8610,12 +8610,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8625,7 +8625,7 @@
         <v>128889846</v>
       </c>
       <c r="B76" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8712,12 +8712,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8936,7 +8936,7 @@
         <v>128889851</v>
       </c>
       <c r="B79" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9043,12 +9043,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10953,7 +10953,7 @@
         <v>128889843</v>
       </c>
       <c r="B97" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11040,12 +11040,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
         <v>128889849</v>
       </c>
       <c r="B121" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13565,12 +13565,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -13580,7 +13580,7 @@
         <v>128889844</v>
       </c>
       <c r="B122" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13667,12 +13667,12 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
@@ -14334,7 +14334,7 @@
         <v>128889853</v>
       </c>
       <c r="B129" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14421,12 +14421,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
@@ -14436,7 +14436,7 @@
         <v>128870907</v>
       </c>
       <c r="B130" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14533,12 +14533,12 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
@@ -16191,7 +16191,7 @@
         <v>128889845</v>
       </c>
       <c r="B146" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16278,12 +16278,12 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -19146,7 +19146,7 @@
         <v>128889841</v>
       </c>
       <c r="B173" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19233,12 +19233,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
@@ -22517,7 +22517,7 @@
         <v>128889842</v>
       </c>
       <c r="B204" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22604,12 +22604,12 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
@@ -22813,7 +22813,7 @@
         <v>128889850</v>
       </c>
       <c r="B207" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22900,12 +22900,12 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
@@ -25880,7 +25880,7 @@
         <v>128889856</v>
       </c>
       <c r="B236" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -25967,12 +25967,12 @@
       <c r="AT236" t="inlineStr"/>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>

--- a/artfynd/A 41147-2025 artfynd.xlsx
+++ b/artfynd/A 41147-2025 artfynd.xlsx
@@ -1203,7 +1203,7 @@
         <v>128889854</v>
       </c>
       <c r="B7" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128869125</v>
       </c>
       <c r="B8" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>128889852</v>
       </c>
       <c r="B9" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>128889848</v>
       </c>
       <c r="B13" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128876118</v>
       </c>
       <c r="B14" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>128878881</v>
       </c>
       <c r="B44" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>128889855</v>
       </c>
       <c r="B62" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>128889847</v>
       </c>
       <c r="B75" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>128889846</v>
       </c>
       <c r="B76" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>128889851</v>
       </c>
       <c r="B79" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>128889843</v>
       </c>
       <c r="B97" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>128889849</v>
       </c>
       <c r="B121" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>128889844</v>
       </c>
       <c r="B122" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>128889853</v>
       </c>
       <c r="B129" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>128870907</v>
       </c>
       <c r="B130" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>128889845</v>
       </c>
       <c r="B146" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>128889841</v>
       </c>
       <c r="B173" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>128889842</v>
       </c>
       <c r="B204" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>128889850</v>
       </c>
       <c r="B207" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>128889856</v>
       </c>
       <c r="B236" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>

--- a/artfynd/A 41147-2025 artfynd.xlsx
+++ b/artfynd/A 41147-2025 artfynd.xlsx
@@ -1203,7 +1203,7 @@
         <v>128889854</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128869125</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>128889852</v>
       </c>
       <c r="B9" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>128889848</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128876118</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>128878881</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>128889855</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>128889847</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>128889846</v>
       </c>
       <c r="B76" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>128889851</v>
       </c>
       <c r="B79" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>128889843</v>
       </c>
       <c r="B97" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>128889849</v>
       </c>
       <c r="B121" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>128889844</v>
       </c>
       <c r="B122" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>128889853</v>
       </c>
       <c r="B129" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>128870907</v>
       </c>
       <c r="B130" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>128889845</v>
       </c>
       <c r="B146" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>128889841</v>
       </c>
       <c r="B173" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>128889842</v>
       </c>
       <c r="B204" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>128889850</v>
       </c>
       <c r="B207" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>128889856</v>
       </c>
       <c r="B236" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>

--- a/artfynd/A 41147-2025 artfynd.xlsx
+++ b/artfynd/A 41147-2025 artfynd.xlsx
@@ -1203,7 +1203,7 @@
         <v>128889854</v>
       </c>
       <c r="B7" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>128869125</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>128889852</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         <v>128889848</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>128876118</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>128878881</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>128889855</v>
       </c>
       <c r="B62" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>128889847</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
         <v>128889846</v>
       </c>
       <c r="B76" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>128889851</v>
       </c>
       <c r="B79" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>128889843</v>
       </c>
       <c r="B97" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>128889849</v>
       </c>
       <c r="B121" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13580,7 +13580,7 @@
         <v>128889844</v>
       </c>
       <c r="B122" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>128889853</v>
       </c>
       <c r="B129" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>128870907</v>
       </c>
       <c r="B130" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16191,7 +16191,7 @@
         <v>128889845</v>
       </c>
       <c r="B146" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>128889841</v>
       </c>
       <c r="B173" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -22517,7 +22517,7 @@
         <v>128889842</v>
       </c>
       <c r="B204" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>128889850</v>
       </c>
       <c r="B207" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -25880,7 +25880,7 @@
         <v>128889856</v>
       </c>
       <c r="B236" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
